--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-01.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,19 +558,15 @@
       <c r="K2" t="n">
         <v>1.28</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -580,78 +576,6 @@
       </c>
       <c r="P2" t="n">
         <v>143</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Internacional de Bogotá x Once Caldas</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Internacional de Bogotá</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Once Caldas</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Lay 2x2 Top 3 (Aprovado)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>LAY</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>GREEN</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>✅ LIQUIDADO</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>coletor (KO-10)</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-01.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-01.xlsx
@@ -558,15 +558,19 @@
       <c r="K2" t="n">
         <v>1.28</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1x3</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>🟢 GREEN</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
